--- a/问题三/results/表1_指定日期购电量.xlsx
+++ b/问题三/results/表1_指定日期购电量.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表1_指定日期购电量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表1_计划购电量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表1_最终购电量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划调整对照" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -763,4 +765,986 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>10:00-10:10时间段</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>10:00-10:10购电量(kWh)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>12:00-12:10时间段</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>12:00-12:10购电量(kWh)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>14:00-14:10时间段</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>14:00-14:10购电量(kWh)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>16:00-16:10时间段</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>16:00-16:10购电量(kWh)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>18:00-18:10时间段</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>18:00-18:10购电量(kWh)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>20:00-20:10时间段</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>20:00-20:10购电量(kWh)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>全天购电量(kWh)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>全天购电费(元)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10:00-10:10</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12:00-12:10</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>769.3563833333333</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>14:00-14:10</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16:00-16:10</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>817.3061166666668</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>18:00-18:10</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>697.9972833333323</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>20:00-20:10</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>69340.33744266667</v>
+      </c>
+      <c r="O2" t="n">
+        <v>57118.27455369173</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10:00-10:10</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12:00-12:10</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>143.8937333333333</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>14:00-14:10</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>16:00-16:10</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>255.2254333333333</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>18:00-18:10</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>20:00-20:10</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>34542.15811666666</v>
+      </c>
+      <c r="O3" t="n">
+        <v>23870.52965051249</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10:00-10:10</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12:00-12:10</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>501.2949833333333</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>14:00-14:10</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>16:00-16:10</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>902.7969499999999</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>18:00-18:10</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>764.3298499999999</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>20:00-20:10</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>68149.93810955966</v>
+      </c>
+      <c r="O4" t="n">
+        <v>57283.97292867616</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10:00-10:10</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12:00-12:10</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1029.411833333333</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>14:00-14:10</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>16:00-16:10</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1001.224</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>18:00-18:10</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>715.41445</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>20:00-20:10</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>94583.89830925924</v>
+      </c>
+      <c r="O5" t="n">
+        <v>71580.43438650476</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>时间段</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>电价(元/kWh)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>计划购电量(kWh)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>最终购电量(kWh)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>调整净变化(kWh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10:00-10:10</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9919</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12:00-12:10</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="D3" t="n">
+        <v>769.3563833333333</v>
+      </c>
+      <c r="E3" t="n">
+        <v>769.3563833333333</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>14:00-14:10</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>16:00-16:10</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8270999999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>817.3061166666668</v>
+      </c>
+      <c r="E5" t="n">
+        <v>817.3061166666668</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>18:00-18:10</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.2561</v>
+      </c>
+      <c r="D6" t="n">
+        <v>697.9972833333333</v>
+      </c>
+      <c r="E6" t="n">
+        <v>697.9972833333323</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-9.094947017729282e-13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20:00-20:10</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1.3513</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10:00-10:10</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9919</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12:00-12:10</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>143.8937333333333</v>
+      </c>
+      <c r="F9" t="n">
+        <v>143.8937333333333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14:00-14:10</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>16:00-16:10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8270999999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>255.2254333333333</v>
+      </c>
+      <c r="E11" t="n">
+        <v>255.2254333333333</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18:00-18:10</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.2561</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20:00-20:10</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1.3513</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10:00-10:10</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9919</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12:00-12:10</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="D15" t="n">
+        <v>501.2949833333333</v>
+      </c>
+      <c r="E15" t="n">
+        <v>501.2949833333333</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14:00-14:10</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>16:00-16:10</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8270999999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>902.7969499999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>902.7969499999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>18:00-18:10</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.2561</v>
+      </c>
+      <c r="D18" t="n">
+        <v>764.3298499999999</v>
+      </c>
+      <c r="E18" t="n">
+        <v>764.3298499999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20:00-20:10</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.3513</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>10:00-10:10</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.9919</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12:00-12:10</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="D21" t="n">
+        <v>962.0869499999999</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1029.411833333333</v>
+      </c>
+      <c r="F21" t="n">
+        <v>67.32488333333345</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>14:00-14:10</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>16:00-16:10</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8270999999999999</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1001.224</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1001.224</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>18:00-18:10</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1.2561</v>
+      </c>
+      <c r="D24" t="n">
+        <v>715.41445</v>
+      </c>
+      <c r="E24" t="n">
+        <v>715.41445</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20:00-20:10</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1.3513</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/问题三/results/表1_指定日期购电量.xlsx
+++ b/问题三/results/表1_指定日期购电量.xlsx
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>769.3563833333333</v>
+        <v>704.0765749999998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>817.3061166666668</v>
+        <v>581.1441958333332</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>697.9972833333333</v>
+        <v>694.0662083333333</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>67445.61404686215</v>
+        <v>69613.19349317592</v>
       </c>
       <c r="O2" t="n">
-        <v>41663.25466204186</v>
+        <v>42678.31295021789</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>255.2254333333333</v>
+        <v>174.76495</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>380.5800713333334</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -634,10 +634,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>33899.99171666666</v>
+        <v>36472.10825992849</v>
       </c>
       <c r="O3" t="n">
-        <v>19522.167056405</v>
+        <v>22225.35344453021</v>
       </c>
     </row>
     <row r="4">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>501.2949833333333</v>
+        <v>497.9872499999999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>902.7969499999999</v>
+        <v>597.9220541666667</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>764.3298499999999</v>
+        <v>578.6872106249992</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>18.5843583333334</v>
       </c>
       <c r="N4" t="n">
-        <v>68149.93810955966</v>
+        <v>70029.95197418414</v>
       </c>
       <c r="O4" t="n">
-        <v>43341.14766613098</v>
+        <v>44993.04206758746</v>
       </c>
     </row>
     <row r="5">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>446.6520375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>962.0869499999999</v>
+        <v>768.6771124999998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1001.224</v>
+        <v>854.3445725639494</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>715.41445</v>
+        <v>675.0119958333331</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>93776.07118950617</v>
+        <v>93129.12472582862</v>
       </c>
       <c r="O5" t="n">
-        <v>59565.76703284562</v>
+        <v>61323.82163026267</v>
       </c>
     </row>
   </sheetData>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>769.3563833333333</v>
+        <v>704.0765749999998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>817.3061166666668</v>
+        <v>581.1441958333332</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>697.9972833333323</v>
+        <v>694.0662083333333</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>69340.33744266667</v>
+        <v>70155.34207884259</v>
       </c>
       <c r="O2" t="n">
-        <v>57118.27455369173</v>
+        <v>43333.27212716051</v>
       </c>
     </row>
     <row r="3">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>143.8937333333333</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>255.2254333333333</v>
+        <v>174.76495</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>380.5800713333334</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>34542.15811666666</v>
+        <v>36472.10825992849</v>
       </c>
       <c r="O3" t="n">
-        <v>23870.52965051249</v>
+        <v>22225.35344453021</v>
       </c>
     </row>
     <row r="4">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>501.2949833333333</v>
+        <v>497.9872499999999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>902.7969499999999</v>
+        <v>597.9220541666667</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>764.3298499999999</v>
+        <v>578.6872106249992</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>18.5843583333334</v>
       </c>
       <c r="N4" t="n">
-        <v>68149.93810955966</v>
+        <v>70073.63832418414</v>
       </c>
       <c r="O4" t="n">
-        <v>57283.97292867616</v>
+        <v>45086.12902399746</v>
       </c>
     </row>
     <row r="5">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>446.6520375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1029.411833333333</v>
+        <v>768.6771124999998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1001.224</v>
+        <v>854.3445725639494</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>715.41445</v>
+        <v>715.8126416666667</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>94583.89830925924</v>
+        <v>93728.07762789755</v>
       </c>
       <c r="O5" t="n">
-        <v>71580.43438650476</v>
+        <v>62491.37074447008</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         <v>0.4411</v>
       </c>
       <c r="D3" t="n">
-        <v>769.3563833333333</v>
+        <v>704.0765749999998</v>
       </c>
       <c r="E3" t="n">
-        <v>769.3563833333333</v>
+        <v>704.0765749999998</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>817.3061166666668</v>
+        <v>581.1441958333332</v>
       </c>
       <c r="E5" t="n">
-        <v>817.3061166666668</v>
+        <v>581.1441958333332</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1279,13 +1279,13 @@
         <v>1.2561</v>
       </c>
       <c r="D6" t="n">
-        <v>697.9972833333333</v>
+        <v>694.0662083333333</v>
       </c>
       <c r="E6" t="n">
-        <v>697.9972833333323</v>
+        <v>694.0662083333333</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1354,10 +1354,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>143.8937333333333</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>143.8937333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1399,10 +1399,10 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>255.2254333333333</v>
+        <v>174.76495</v>
       </c>
       <c r="E11" t="n">
-        <v>255.2254333333333</v>
+        <v>174.76495</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1.2561</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>380.5800713333334</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>380.5800713333334</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1495,10 +1495,10 @@
         <v>0.4411</v>
       </c>
       <c r="D15" t="n">
-        <v>501.2949833333333</v>
+        <v>497.9872499999999</v>
       </c>
       <c r="E15" t="n">
-        <v>501.2949833333333</v>
+        <v>497.9872499999999</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>902.7969499999999</v>
+        <v>597.9220541666667</v>
       </c>
       <c r="E17" t="n">
-        <v>902.7969499999999</v>
+        <v>597.9220541666667</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1567,10 +1567,10 @@
         <v>1.2561</v>
       </c>
       <c r="D18" t="n">
-        <v>764.3298499999999</v>
+        <v>578.6872106249992</v>
       </c>
       <c r="E18" t="n">
-        <v>764.3298499999999</v>
+        <v>578.6872106249992</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
         <v>1.3513</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>18.5843583333334</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>18.5843583333334</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1615,10 +1615,10 @@
         <v>0.9919</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>446.6520375</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>446.6520375</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1639,13 +1639,13 @@
         <v>0.4411</v>
       </c>
       <c r="D21" t="n">
-        <v>962.0869499999999</v>
+        <v>768.6771124999998</v>
       </c>
       <c r="E21" t="n">
-        <v>1029.411833333333</v>
+        <v>768.6771124999998</v>
       </c>
       <c r="F21" t="n">
-        <v>67.32488333333345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1687,10 +1687,10 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>1001.224</v>
+        <v>854.3445725639494</v>
       </c>
       <c r="E23" t="n">
-        <v>1001.224</v>
+        <v>854.3445725639494</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1711,13 +1711,13 @@
         <v>1.2561</v>
       </c>
       <c r="D24" t="n">
-        <v>715.41445</v>
+        <v>675.0119958333331</v>
       </c>
       <c r="E24" t="n">
-        <v>715.41445</v>
+        <v>715.8126416666667</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>40.80064583333353</v>
       </c>
     </row>
     <row r="25">

--- a/问题三/results/表1_指定日期购电量.xlsx
+++ b/问题三/results/表1_指定日期购电量.xlsx
@@ -573,10 +573,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>69613.19349317592</v>
+        <v>67439.61595818795</v>
       </c>
       <c r="O2" t="n">
-        <v>42678.31295021789</v>
+        <v>41708.3680995156</v>
       </c>
     </row>
     <row r="3">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>380.5800713333334</v>
+        <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -634,10 +634,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>36472.10825992849</v>
+        <v>35990.10046714616</v>
       </c>
       <c r="O3" t="n">
-        <v>22225.35344453021</v>
+        <v>21884.94369969972</v>
       </c>
     </row>
     <row r="4">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>578.6872106249992</v>
+        <v>668.3980666666665</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -695,10 +695,10 @@
         <v>18.5843583333334</v>
       </c>
       <c r="N4" t="n">
-        <v>70029.95197418414</v>
+        <v>68213.01807778841</v>
       </c>
       <c r="O4" t="n">
-        <v>44993.04206758746</v>
+        <v>44123.78746673523</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>854.3445725639494</v>
+        <v>864.9261458333331</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>93129.12472582862</v>
+        <v>93419.00366283522</v>
       </c>
       <c r="O5" t="n">
-        <v>61323.82163026267</v>
+        <v>61468.77392504711</v>
       </c>
     </row>
   </sheetData>
@@ -925,10 +925,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>70155.34207884259</v>
+        <v>67439.61595818795</v>
       </c>
       <c r="O2" t="n">
-        <v>43333.27212716051</v>
+        <v>43714.79073757254</v>
       </c>
     </row>
     <row r="3">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>380.5800713333334</v>
+        <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>36472.10825992849</v>
+        <v>35990.10046714616</v>
       </c>
       <c r="O3" t="n">
-        <v>22225.35344453021</v>
+        <v>21884.94369969972</v>
       </c>
     </row>
     <row r="4">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>578.6872106249992</v>
+        <v>668.3980666666665</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         <v>18.5843583333334</v>
       </c>
       <c r="N4" t="n">
-        <v>70073.63832418414</v>
+        <v>68172.9505717571</v>
       </c>
       <c r="O4" t="n">
-        <v>45086.12902399746</v>
+        <v>44191.86991976143</v>
       </c>
     </row>
     <row r="5">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>768.6771124999998</v>
+        <v>941.2526416666665</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>854.3445725639494</v>
+        <v>864.9261458333331</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>715.8126416666667</v>
+        <v>675.0119958333331</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>93728.07762789755</v>
+        <v>95502.58920908008</v>
       </c>
       <c r="O5" t="n">
-        <v>62491.37074447008</v>
+        <v>63192.574996512</v>
       </c>
     </row>
   </sheetData>
@@ -1423,10 +1423,10 @@
         <v>1.2561</v>
       </c>
       <c r="D12" t="n">
-        <v>380.5800713333334</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>380.5800713333334</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1567,10 +1567,10 @@
         <v>1.2561</v>
       </c>
       <c r="D18" t="n">
-        <v>578.6872106249992</v>
+        <v>668.3980666666665</v>
       </c>
       <c r="E18" t="n">
-        <v>578.6872106249992</v>
+        <v>668.3980666666665</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1642,10 +1642,10 @@
         <v>768.6771124999998</v>
       </c>
       <c r="E21" t="n">
-        <v>768.6771124999998</v>
+        <v>941.2526416666665</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>172.5755291666667</v>
       </c>
     </row>
     <row r="22">
@@ -1687,10 +1687,10 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>854.3445725639494</v>
+        <v>864.9261458333331</v>
       </c>
       <c r="E23" t="n">
-        <v>854.3445725639494</v>
+        <v>864.9261458333331</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1714,10 +1714,10 @@
         <v>675.0119958333331</v>
       </c>
       <c r="E24" t="n">
-        <v>715.8126416666667</v>
+        <v>675.0119958333331</v>
       </c>
       <c r="F24" t="n">
-        <v>40.80064583333353</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
